--- a/The Complete Financial Analyst Course/Section 5/48. Key Excel Functions SUM, SUMIF, SUMIFS/39.+Sum-Sumif-Sumifs-Lecture+-+Solved.xlsx
+++ b/The Complete Financial Analyst Course/Section 5/48. Key Excel Functions SUM, SUMIF, SUMIFS/39.+Sum-Sumif-Sumifs-Lecture+-+Solved.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NewPC\Desktop\Courses\Video creating\The Complete Financial Analyst Course\Resources\5. Beginner, Intermediate &amp; Advanced Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\economics\udemy_economics\The Complete Financial Analyst Course\Section 5\48. Key Excel Functions SUM, SUMIF, SUMIFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DDB106-632F-46E6-BEEA-04AB042195C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="28680" yWindow="270" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sum" sheetId="1" r:id="rId1"/>
     <sheet name="Sumif" sheetId="2" r:id="rId2"/>
     <sheet name="Sumifs" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -100,7 +112,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -534,7 +546,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F13"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
@@ -743,7 +755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:F18"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
@@ -962,8 +974,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B1:F17"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
@@ -1177,6 +1189,12 @@
         <v>143</v>
       </c>
     </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="2">
+        <f>SUMIFS(F4:F12,C4:C12,C16,D4:D12,D16)</f>
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
